--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R407"/>
+  <dimension ref="A1:R409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24855,6 +24855,126 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="C408" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="D408" t="n">
+        <v>374.46</v>
+      </c>
+      <c r="E408" t="n">
+        <v>377.8</v>
+      </c>
+      <c r="F408" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="G408" t="n">
+        <v>381.24</v>
+      </c>
+      <c r="H408" t="n">
+        <v>381.45</v>
+      </c>
+      <c r="I408" t="n">
+        <v>384.11</v>
+      </c>
+      <c r="J408" t="n">
+        <v>385.19</v>
+      </c>
+      <c r="K408" t="n">
+        <v>385.9</v>
+      </c>
+      <c r="L408" t="n">
+        <v>376.99</v>
+      </c>
+      <c r="M408" t="n">
+        <v>376.28</v>
+      </c>
+      <c r="N408" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="O408" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="P408" t="n">
+        <v>372.84</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="C409" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="D409" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="E409" t="n">
+        <v>375.36</v>
+      </c>
+      <c r="F409" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="G409" t="n">
+        <v>379.53</v>
+      </c>
+      <c r="H409" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="I409" t="n">
+        <v>381.84</v>
+      </c>
+      <c r="J409" t="n">
+        <v>383.23</v>
+      </c>
+      <c r="K409" t="n">
+        <v>384.46</v>
+      </c>
+      <c r="L409" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="M409" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="N409" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="O409" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="P409" t="n">
+        <v>372.84</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24866,7 +24986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B433"/>
+  <dimension ref="A1:B435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29199,6 +29319,26 @@
       </c>
       <c r="B433" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -29367,28 +29507,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3676136296422619</v>
+        <v>0.3618667884543715</v>
       </c>
       <c r="J2" t="n">
+        <v>408</v>
+      </c>
+      <c r="K2" t="n">
         <v>406</v>
       </c>
-      <c r="K2" t="n">
-        <v>404</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.190035981701862</v>
+        <v>0.1860311138974386</v>
       </c>
       <c r="M2" t="n">
-        <v>4.223478031362838</v>
+        <v>4.233602345370024</v>
       </c>
       <c r="N2" t="n">
-        <v>30.9271928088338</v>
+        <v>30.96012492041627</v>
       </c>
       <c r="O2" t="n">
-        <v>5.561222240554121</v>
+        <v>5.564182322715196</v>
       </c>
       <c r="P2" t="n">
-        <v>355.349815823739</v>
+        <v>355.4089006405213</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29445,28 +29585,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5575690932255869</v>
+        <v>0.5508649632625352</v>
       </c>
       <c r="J3" t="n">
+        <v>408</v>
+      </c>
+      <c r="K3" t="n">
         <v>406</v>
       </c>
-      <c r="K3" t="n">
-        <v>404</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3676493588107701</v>
+        <v>0.3626892621532715</v>
       </c>
       <c r="M3" t="n">
-        <v>4.152966663037989</v>
+        <v>4.166904061023408</v>
       </c>
       <c r="N3" t="n">
-        <v>28.71104099948401</v>
+        <v>28.81309251543488</v>
       </c>
       <c r="O3" t="n">
-        <v>5.358268470269477</v>
+        <v>5.367782830502263</v>
       </c>
       <c r="P3" t="n">
-        <v>356.0508638953341</v>
+        <v>356.1197892142354</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29523,28 +29663,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3574677538899539</v>
+        <v>0.3534285018126994</v>
       </c>
       <c r="J4" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K4" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2415114836875883</v>
+        <v>0.2387207143680218</v>
       </c>
       <c r="M4" t="n">
-        <v>3.483311795266594</v>
+        <v>3.484414424138573</v>
       </c>
       <c r="N4" t="n">
-        <v>21.5051347222171</v>
+        <v>21.48225378957105</v>
       </c>
       <c r="O4" t="n">
-        <v>4.637362906029363</v>
+        <v>4.634895229621814</v>
       </c>
       <c r="P4" t="n">
-        <v>368.0405426133677</v>
+        <v>368.0820891213345</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29601,28 +29741,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4399883562480843</v>
+        <v>0.4376653379711191</v>
       </c>
       <c r="J5" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K5" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2917985786922231</v>
+        <v>0.2916732552621073</v>
       </c>
       <c r="M5" t="n">
-        <v>3.698451204891458</v>
+        <v>3.689803111094105</v>
       </c>
       <c r="N5" t="n">
-        <v>25.1775339186052</v>
+        <v>25.08673448399073</v>
       </c>
       <c r="O5" t="n">
-        <v>5.017721984985338</v>
+        <v>5.008665938549978</v>
       </c>
       <c r="P5" t="n">
-        <v>367.3402255796509</v>
+        <v>367.3641224460422</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29679,28 +29819,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4125832483433574</v>
+        <v>0.4128374093324335</v>
       </c>
       <c r="J6" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K6" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3336771070830664</v>
+        <v>0.3363855605063942</v>
       </c>
       <c r="M6" t="n">
-        <v>3.230510597919679</v>
+        <v>3.220332742496082</v>
       </c>
       <c r="N6" t="n">
-        <v>18.21539970000212</v>
+        <v>18.13257014633593</v>
       </c>
       <c r="O6" t="n">
-        <v>4.267950292588015</v>
+        <v>4.258235567266792</v>
       </c>
       <c r="P6" t="n">
-        <v>367.4113551473651</v>
+        <v>367.4087467782821</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29757,28 +29897,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4531402708687132</v>
+        <v>0.45540250975965</v>
       </c>
       <c r="J7" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3618836350200955</v>
+        <v>0.3664700943078794</v>
       </c>
       <c r="M7" t="n">
-        <v>3.176350730154707</v>
+        <v>3.172732714960947</v>
       </c>
       <c r="N7" t="n">
-        <v>19.4023108887951</v>
+        <v>19.33491272745512</v>
       </c>
       <c r="O7" t="n">
-        <v>4.404805431434526</v>
+        <v>4.397148249428842</v>
       </c>
       <c r="P7" t="n">
-        <v>366.2579251091941</v>
+        <v>366.2346634333581</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29835,28 +29975,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3800960485198086</v>
+        <v>0.3858638493346945</v>
       </c>
       <c r="J8" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K8" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3126138214052377</v>
+        <v>0.3195178439584385</v>
       </c>
       <c r="M8" t="n">
-        <v>3.268343272275529</v>
+        <v>3.281957676861743</v>
       </c>
       <c r="N8" t="n">
-        <v>17.02301689887199</v>
+        <v>17.10064949118956</v>
       </c>
       <c r="O8" t="n">
-        <v>4.125895890454823</v>
+        <v>4.135293156620164</v>
       </c>
       <c r="P8" t="n">
-        <v>364.9488956721102</v>
+        <v>364.889581066561</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29913,28 +30053,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3095751080575684</v>
+        <v>0.317972653122565</v>
       </c>
       <c r="J9" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K9" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1903013875141345</v>
+        <v>0.1980058058446675</v>
       </c>
       <c r="M9" t="n">
-        <v>3.637445500015178</v>
+        <v>3.664544714406067</v>
       </c>
       <c r="N9" t="n">
-        <v>21.85096932577054</v>
+        <v>22.08491016234751</v>
       </c>
       <c r="O9" t="n">
-        <v>4.674502040407142</v>
+        <v>4.699458496715074</v>
       </c>
       <c r="P9" t="n">
-        <v>366.5317347646943</v>
+        <v>366.4453762963168</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29991,28 +30131,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2550361146090323</v>
+        <v>0.2645476229555679</v>
       </c>
       <c r="J10" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K10" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L10" t="n">
-        <v>0.171475684638855</v>
+        <v>0.1800118069039619</v>
       </c>
       <c r="M10" t="n">
-        <v>3.280238467183533</v>
+        <v>3.312291744726329</v>
       </c>
       <c r="N10" t="n">
-        <v>16.84082180755224</v>
+        <v>17.1924247117581</v>
       </c>
       <c r="O10" t="n">
-        <v>4.10375703563847</v>
+        <v>4.146374887990484</v>
       </c>
       <c r="P10" t="n">
-        <v>368.092967913749</v>
+        <v>367.9951521786739</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30069,28 +30209,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2204673464868585</v>
+        <v>0.2319898618801088</v>
       </c>
       <c r="J11" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K11" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1264366445314192</v>
+        <v>0.1353574494807581</v>
       </c>
       <c r="M11" t="n">
-        <v>3.440495314301208</v>
+        <v>3.484201925056416</v>
       </c>
       <c r="N11" t="n">
-        <v>17.9956358694069</v>
+        <v>18.54023567683724</v>
       </c>
       <c r="O11" t="n">
-        <v>4.242126338218476</v>
+        <v>4.305837395540761</v>
       </c>
       <c r="P11" t="n">
-        <v>367.9808925015816</v>
+        <v>367.8623934388695</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30147,28 +30287,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2047332820499075</v>
+        <v>0.2131573259572709</v>
       </c>
       <c r="J12" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K12" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0815091016066336</v>
+        <v>0.08759355056221352</v>
       </c>
       <c r="M12" t="n">
-        <v>4.249782084568569</v>
+        <v>4.264189050298365</v>
       </c>
       <c r="N12" t="n">
-        <v>25.31062379178891</v>
+        <v>25.52345947795678</v>
       </c>
       <c r="O12" t="n">
-        <v>5.030966486848119</v>
+        <v>5.05207476963245</v>
       </c>
       <c r="P12" t="n">
-        <v>363.0498783423489</v>
+        <v>362.9632429013976</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30225,28 +30365,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2143321140312557</v>
+        <v>0.2257213498805915</v>
       </c>
       <c r="J13" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K13" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08473167598951836</v>
+        <v>0.09211696555241156</v>
       </c>
       <c r="M13" t="n">
-        <v>4.368470744353522</v>
+        <v>4.398260142584191</v>
       </c>
       <c r="N13" t="n">
-        <v>26.59097926949159</v>
+        <v>27.0806042762395</v>
       </c>
       <c r="O13" t="n">
-        <v>5.156644186822627</v>
+        <v>5.20390279273542</v>
       </c>
       <c r="P13" t="n">
-        <v>358.4340097389359</v>
+        <v>358.3168824190976</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30303,28 +30443,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1565930186728242</v>
+        <v>0.1656624708231814</v>
       </c>
       <c r="J14" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K14" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04145770296064899</v>
+        <v>0.04609910272685014</v>
       </c>
       <c r="M14" t="n">
-        <v>4.712395645792962</v>
+        <v>4.728665506772447</v>
       </c>
       <c r="N14" t="n">
-        <v>30.62418132823117</v>
+        <v>30.86919790284268</v>
       </c>
       <c r="O14" t="n">
-        <v>5.533911937159027</v>
+        <v>5.556005570807383</v>
       </c>
       <c r="P14" t="n">
-        <v>352.5450791705574</v>
+        <v>352.4523446119705</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30381,28 +30521,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.249482128701018</v>
+        <v>0.2608394486733936</v>
       </c>
       <c r="J15" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K15" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08125689701887695</v>
+        <v>0.08775566717826622</v>
       </c>
       <c r="M15" t="n">
-        <v>5.26736977421821</v>
+        <v>5.287225211715306</v>
       </c>
       <c r="N15" t="n">
-        <v>38.01249617006209</v>
+        <v>38.44579447756963</v>
       </c>
       <c r="O15" t="n">
-        <v>6.165427492888234</v>
+        <v>6.200467278969355</v>
       </c>
       <c r="P15" t="n">
-        <v>350.4935991763729</v>
+        <v>350.3774713208762</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30459,28 +30599,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2233735278279598</v>
+        <v>0.2371068963869856</v>
       </c>
       <c r="J16" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K16" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05189038859397199</v>
+        <v>0.05769962063580159</v>
       </c>
       <c r="M16" t="n">
-        <v>5.808719084777741</v>
+        <v>5.833056435309091</v>
       </c>
       <c r="N16" t="n">
-        <v>49.24347380989968</v>
+        <v>49.90810395790465</v>
       </c>
       <c r="O16" t="n">
-        <v>7.017369436612246</v>
+        <v>7.064566791948722</v>
       </c>
       <c r="P16" t="n">
-        <v>353.2757395720879</v>
+        <v>353.1353167707194</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30537,28 +30677,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1564570001168241</v>
+        <v>0.1737341277745876</v>
       </c>
       <c r="J17" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K17" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02027011620007146</v>
+        <v>0.02460999668606523</v>
       </c>
       <c r="M17" t="n">
-        <v>6.644484019286589</v>
+        <v>6.681620055435408</v>
       </c>
       <c r="N17" t="n">
-        <v>63.9077847714015</v>
+        <v>65.02843655478358</v>
       </c>
       <c r="O17" t="n">
-        <v>7.994234470629536</v>
+        <v>8.064021115720344</v>
       </c>
       <c r="P17" t="n">
-        <v>353.0423049111849</v>
+        <v>352.8656473966515</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30596,7 +30736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R407"/>
+  <dimension ref="A1:R409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67987,6 +68127,190 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-36.835712903756296,175.802259866542</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-36.83606613664482,175.80304288304725</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-36.83639502009893,175.80384467322128</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-36.836759426827456,175.8046190696976</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-36.83713671337239,175.8053870844684</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-36.83753250945246,175.80614162580156</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-36.83794328810394,175.80688019453342</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-36.83833357096072,175.8076298186501</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-36.83871690483243,175.80838057556656</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-36.83909036778209,175.8091440592155</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>-36.839540092654694,175.8098562958633</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>-36.83993476294788,175.81060897813435</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>-36.840405618750395,175.81130464822672</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>-36.84082250666711,175.81204017825544</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>-36.84124949800514,175.8127617459061</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>-36.841670024417404,175.81348592128717</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-36.835749424376345,175.80223170535925</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-36.8361035761355,175.80301401354922</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-36.836411021895124,175.803832334387</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-36.83677810840563,175.8046046646179</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-36.83715394503068,175.8053733897119</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>-36.837545335818035,175.80613101491755</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-36.83795547590326,175.80687000835644</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-36.83835070647559,175.8076159382785</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-36.838731948571194,175.80836907913152</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-36.83910150044094,175.80913577728808</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>-36.83954355718337,175.80985367796592</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>-36.83994909884218,175.8105979749962</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>-36.840405618750395,175.81130464822672</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>-36.84082250666711,175.81204017825544</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>-36.84124949800514,175.8127617459061</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>-36.841670024417404,175.81348592128717</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R409"/>
+  <dimension ref="A1:R410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24975,6 +24975,66 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="C410" t="n">
+        <v>358.13</v>
+      </c>
+      <c r="D410" t="n">
+        <v>369.94</v>
+      </c>
+      <c r="E410" t="n">
+        <v>374.2</v>
+      </c>
+      <c r="F410" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="G410" t="n">
+        <v>377.89</v>
+      </c>
+      <c r="H410" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="I410" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="J410" t="n">
+        <v>381.93</v>
+      </c>
+      <c r="K410" t="n">
+        <v>383.19</v>
+      </c>
+      <c r="L410" t="n">
+        <v>376.26</v>
+      </c>
+      <c r="M410" t="n">
+        <v>373.53</v>
+      </c>
+      <c r="N410" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="O410" t="n">
+        <v>367.18</v>
+      </c>
+      <c r="P410" t="n">
+        <v>371.45</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24986,7 +25046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B435"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29339,6 +29399,16 @@
       </c>
       <c r="B435" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -29507,28 +29577,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3618667884543715</v>
+        <v>0.3557479382395959</v>
       </c>
       <c r="J2" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1860311138974386</v>
+        <v>0.1800428148838848</v>
       </c>
       <c r="M2" t="n">
-        <v>4.233602345370024</v>
+        <v>4.255864279839521</v>
       </c>
       <c r="N2" t="n">
-        <v>30.96012492041627</v>
+        <v>31.24352066764989</v>
       </c>
       <c r="O2" t="n">
-        <v>5.564182322715196</v>
+        <v>5.589590384603319</v>
       </c>
       <c r="P2" t="n">
-        <v>355.4089006405213</v>
+        <v>355.4720033167711</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29585,28 +29655,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5508649632625352</v>
+        <v>0.5445768902584682</v>
       </c>
       <c r="J3" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3626892621532715</v>
+        <v>0.3556801907149911</v>
       </c>
       <c r="M3" t="n">
-        <v>4.166904061023408</v>
+        <v>4.189014909760033</v>
       </c>
       <c r="N3" t="n">
-        <v>28.81309251543488</v>
+        <v>29.12192116863999</v>
       </c>
       <c r="O3" t="n">
-        <v>5.367782830502263</v>
+        <v>5.396473030474626</v>
       </c>
       <c r="P3" t="n">
-        <v>356.1197892142354</v>
+        <v>356.1846370567357</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29663,28 +29733,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3534285018126994</v>
+        <v>0.3496770095887513</v>
       </c>
       <c r="J4" t="n">
+        <v>409</v>
+      </c>
+      <c r="K4" t="n">
         <v>408</v>
       </c>
-      <c r="K4" t="n">
-        <v>407</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2387207143680218</v>
+        <v>0.2347502036358881</v>
       </c>
       <c r="M4" t="n">
-        <v>3.484414424138573</v>
+        <v>3.492920177998569</v>
       </c>
       <c r="N4" t="n">
-        <v>21.48225378957105</v>
+        <v>21.56432785304157</v>
       </c>
       <c r="O4" t="n">
-        <v>4.634895229621814</v>
+        <v>4.643740717680259</v>
       </c>
       <c r="P4" t="n">
-        <v>368.0820891213345</v>
+        <v>368.1207966904065</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29741,28 +29811,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4376653379711191</v>
+        <v>0.4353066530097467</v>
       </c>
       <c r="J5" t="n">
+        <v>409</v>
+      </c>
+      <c r="K5" t="n">
         <v>408</v>
       </c>
-      <c r="K5" t="n">
-        <v>407</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2916732552621073</v>
+        <v>0.2901677809364757</v>
       </c>
       <c r="M5" t="n">
-        <v>3.689803111094105</v>
+        <v>3.690372329346591</v>
       </c>
       <c r="N5" t="n">
-        <v>25.08673448399073</v>
+        <v>25.07850544126538</v>
       </c>
       <c r="O5" t="n">
-        <v>5.008665938549978</v>
+        <v>5.007844390680024</v>
       </c>
       <c r="P5" t="n">
-        <v>367.3641224460422</v>
+        <v>367.3884591514413</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29819,28 +29889,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4128374093324335</v>
+        <v>0.4118302345383447</v>
       </c>
       <c r="J6" t="n">
+        <v>409</v>
+      </c>
+      <c r="K6" t="n">
         <v>408</v>
       </c>
-      <c r="K6" t="n">
-        <v>407</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3363855605063942</v>
+        <v>0.3364332378898818</v>
       </c>
       <c r="M6" t="n">
-        <v>3.220332742496082</v>
+        <v>3.216898330803635</v>
       </c>
       <c r="N6" t="n">
-        <v>18.13257014633593</v>
+        <v>18.09783837435262</v>
       </c>
       <c r="O6" t="n">
-        <v>4.258235567266792</v>
+        <v>4.25415542432956</v>
       </c>
       <c r="P6" t="n">
-        <v>367.4087467782821</v>
+        <v>367.4191387198302</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29897,28 +29967,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.45540250975965</v>
+        <v>0.4552399933173514</v>
       </c>
       <c r="J7" t="n">
+        <v>409</v>
+      </c>
+      <c r="K7" t="n">
         <v>408</v>
       </c>
-      <c r="K7" t="n">
-        <v>407</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.3664700943078794</v>
+        <v>0.3676104605013079</v>
       </c>
       <c r="M7" t="n">
-        <v>3.172732714960947</v>
+        <v>3.165653778792467</v>
       </c>
       <c r="N7" t="n">
-        <v>19.33491272745512</v>
+        <v>19.28777607211645</v>
       </c>
       <c r="O7" t="n">
-        <v>4.397148249428842</v>
+        <v>4.391785066703112</v>
       </c>
       <c r="P7" t="n">
-        <v>366.2346634333581</v>
+        <v>366.2363402638139</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29975,28 +30045,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3858638493346945</v>
+        <v>0.3879284631735515</v>
       </c>
       <c r="J8" t="n">
+        <v>409</v>
+      </c>
+      <c r="K8" t="n">
         <v>408</v>
       </c>
-      <c r="K8" t="n">
-        <v>407</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3195178439584385</v>
+        <v>0.3225517788161303</v>
       </c>
       <c r="M8" t="n">
-        <v>3.281957676861743</v>
+        <v>3.284709208190252</v>
       </c>
       <c r="N8" t="n">
-        <v>17.10064949118956</v>
+        <v>17.0995420444699</v>
       </c>
       <c r="O8" t="n">
-        <v>4.135293156620164</v>
+        <v>4.135159252612878</v>
       </c>
       <c r="P8" t="n">
-        <v>364.889581066561</v>
+        <v>364.8682785613168</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30053,28 +30123,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.317972653122565</v>
+        <v>0.321335838476042</v>
       </c>
       <c r="J9" t="n">
+        <v>409</v>
+      </c>
+      <c r="K9" t="n">
         <v>408</v>
       </c>
-      <c r="K9" t="n">
-        <v>407</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1980058058446675</v>
+        <v>0.2014864931261399</v>
       </c>
       <c r="M9" t="n">
-        <v>3.664544714406067</v>
+        <v>3.673671956575456</v>
       </c>
       <c r="N9" t="n">
-        <v>22.08491016234751</v>
+        <v>22.13906017064682</v>
       </c>
       <c r="O9" t="n">
-        <v>4.699458496715074</v>
+        <v>4.705216272462597</v>
       </c>
       <c r="P9" t="n">
-        <v>366.4453762963168</v>
+        <v>366.4106752436156</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30131,28 +30201,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2645476229555679</v>
+        <v>0.2680631286284746</v>
       </c>
       <c r="J10" t="n">
+        <v>409</v>
+      </c>
+      <c r="K10" t="n">
         <v>408</v>
       </c>
-      <c r="K10" t="n">
-        <v>407</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1800118069039619</v>
+        <v>0.1837560424263601</v>
       </c>
       <c r="M10" t="n">
-        <v>3.312291744726329</v>
+        <v>3.322174253034818</v>
       </c>
       <c r="N10" t="n">
-        <v>17.1924247117581</v>
+        <v>17.26859629324926</v>
       </c>
       <c r="O10" t="n">
-        <v>4.146374887990484</v>
+        <v>4.155550059047449</v>
       </c>
       <c r="P10" t="n">
-        <v>367.9951521786739</v>
+        <v>367.958879498222</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30209,28 +30279,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2319898618801088</v>
+        <v>0.2366413796121759</v>
       </c>
       <c r="J11" t="n">
+        <v>409</v>
+      </c>
+      <c r="K11" t="n">
         <v>408</v>
       </c>
-      <c r="K11" t="n">
-        <v>407</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1353574494807581</v>
+        <v>0.1394105725799842</v>
       </c>
       <c r="M11" t="n">
-        <v>3.484201925056416</v>
+        <v>3.500170732500401</v>
       </c>
       <c r="N11" t="n">
-        <v>18.54023567683724</v>
+        <v>18.70191999022286</v>
       </c>
       <c r="O11" t="n">
-        <v>4.305837395540761</v>
+        <v>4.324571653958674</v>
       </c>
       <c r="P11" t="n">
-        <v>367.8623934388695</v>
+        <v>367.8143994852224</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30287,28 +30357,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2131573259572709</v>
+        <v>0.2170310861334483</v>
       </c>
       <c r="J12" t="n">
+        <v>409</v>
+      </c>
+      <c r="K12" t="n">
         <v>408</v>
       </c>
-      <c r="K12" t="n">
-        <v>407</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.08759355056221352</v>
+        <v>0.0905161722644362</v>
       </c>
       <c r="M12" t="n">
-        <v>4.264189050298365</v>
+        <v>4.270410418126224</v>
       </c>
       <c r="N12" t="n">
-        <v>25.52345947795678</v>
+        <v>25.60455370845554</v>
       </c>
       <c r="O12" t="n">
-        <v>5.05207476963245</v>
+        <v>5.060094239088392</v>
       </c>
       <c r="P12" t="n">
-        <v>362.9632429013976</v>
+        <v>362.9232737822746</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30365,28 +30435,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2257213498805915</v>
+        <v>0.2303949101707662</v>
       </c>
       <c r="J13" t="n">
+        <v>409</v>
+      </c>
+      <c r="K13" t="n">
         <v>408</v>
       </c>
-      <c r="K13" t="n">
-        <v>407</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09211696555241156</v>
+        <v>0.09542331914595104</v>
       </c>
       <c r="M13" t="n">
-        <v>4.398260142584191</v>
+        <v>4.409000962126948</v>
       </c>
       <c r="N13" t="n">
-        <v>27.0806042762395</v>
+        <v>27.22332401809041</v>
       </c>
       <c r="O13" t="n">
-        <v>5.20390279273542</v>
+        <v>5.217597533165088</v>
       </c>
       <c r="P13" t="n">
-        <v>358.3168824190976</v>
+        <v>358.2686610322614</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30443,28 +30513,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1656624708231814</v>
+        <v>0.1692687815255825</v>
       </c>
       <c r="J14" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K14" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04609910272685014</v>
+        <v>0.0481006877477903</v>
       </c>
       <c r="M14" t="n">
-        <v>4.728665506772447</v>
+        <v>4.732603368535835</v>
       </c>
       <c r="N14" t="n">
-        <v>30.86919790284268</v>
+        <v>30.91968146868032</v>
       </c>
       <c r="O14" t="n">
-        <v>5.556005570807383</v>
+        <v>5.560546867771219</v>
       </c>
       <c r="P14" t="n">
-        <v>352.4523446119705</v>
+        <v>352.4153494366698</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30521,28 +30591,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2608394486733936</v>
+        <v>0.2658156208711207</v>
       </c>
       <c r="J15" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K15" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08775566717826622</v>
+        <v>0.09077778713841911</v>
       </c>
       <c r="M15" t="n">
-        <v>5.287225211715306</v>
+        <v>5.294100314764722</v>
       </c>
       <c r="N15" t="n">
-        <v>38.44579447756963</v>
+        <v>38.59161839163628</v>
       </c>
       <c r="O15" t="n">
-        <v>6.200467278969355</v>
+        <v>6.212215256382885</v>
       </c>
       <c r="P15" t="n">
-        <v>350.3774713208762</v>
+        <v>350.3264234833567</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30599,28 +30669,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2371068963869856</v>
+        <v>0.2431507652079896</v>
       </c>
       <c r="J16" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K16" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05769962063580159</v>
+        <v>0.06041513479758365</v>
       </c>
       <c r="M16" t="n">
-        <v>5.833056435309091</v>
+        <v>5.842078784581035</v>
       </c>
       <c r="N16" t="n">
-        <v>49.90810395790465</v>
+        <v>50.13985726410161</v>
       </c>
       <c r="O16" t="n">
-        <v>7.064566791948722</v>
+        <v>7.08095030798138</v>
       </c>
       <c r="P16" t="n">
-        <v>353.1353167707194</v>
+        <v>353.0733160156602</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30677,28 +30747,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1737341277745876</v>
+        <v>0.1813086437486558</v>
       </c>
       <c r="J17" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K17" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02460999668606523</v>
+        <v>0.02666828068416005</v>
       </c>
       <c r="M17" t="n">
-        <v>6.681620055435408</v>
+        <v>6.695808955366645</v>
       </c>
       <c r="N17" t="n">
-        <v>65.02843655478358</v>
+        <v>65.42510462998048</v>
       </c>
       <c r="O17" t="n">
-        <v>8.064021115720344</v>
+        <v>8.088578653260441</v>
       </c>
       <c r="P17" t="n">
-        <v>352.8656473966515</v>
+        <v>352.7879445669726</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30736,7 +30806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R409"/>
+  <dimension ref="A1:R410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68311,6 +68381,98 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-36.835781044950494,175.80220732259505</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-36.836130067059806,175.80299358644402</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-36.83642962685294,175.803817988272</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-36.83678698981112,175.8045978162989</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-36.83716214335222,175.80536687414278</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-36.837557637126956,175.806120838394</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-36.83796056038372,175.80686575890743</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-36.83835342400205,175.80761373698553</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-36.838741926560665,175.80836145394258</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-36.83911131882714,175.80912847308622</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>-36.839545712890086,175.80985204905187</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>-36.83995584514508,175.81059279704746</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>-36.84041817544783,175.81129414016232</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>-36.840831021525744,175.81203207715797</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>-36.841259455221,175.81275230163277</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>-36.84168328528589,175.81347392864032</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R410"/>
+  <dimension ref="A1:R411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25035,6 +25035,66 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>353.73</v>
+      </c>
+      <c r="C411" t="n">
+        <v>357.97</v>
+      </c>
+      <c r="D411" t="n">
+        <v>370.96</v>
+      </c>
+      <c r="E411" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="F411" t="n">
+        <v>375.85</v>
+      </c>
+      <c r="G411" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="H411" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="I411" t="n">
+        <v>380.29</v>
+      </c>
+      <c r="J411" t="n">
+        <v>379.95</v>
+      </c>
+      <c r="K411" t="n">
+        <v>379.83</v>
+      </c>
+      <c r="L411" t="n">
+        <v>373.68</v>
+      </c>
+      <c r="M411" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="N411" t="n">
+        <v>361.72</v>
+      </c>
+      <c r="O411" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="P411" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>371.87</v>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25046,7 +25106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B436"/>
+  <dimension ref="A1:B437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29409,6 +29469,16 @@
       </c>
       <c r="B436" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -29577,28 +29647,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3557479382395959</v>
+        <v>0.350139107294283</v>
       </c>
       <c r="J2" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1800428148838848</v>
+        <v>0.1748253345102537</v>
       </c>
       <c r="M2" t="n">
-        <v>4.255864279839521</v>
+        <v>4.275120533052866</v>
       </c>
       <c r="N2" t="n">
-        <v>31.24352066764989</v>
+        <v>31.46839228503618</v>
       </c>
       <c r="O2" t="n">
-        <v>5.589590384603319</v>
+        <v>5.609669534387582</v>
       </c>
       <c r="P2" t="n">
-        <v>355.4720033167711</v>
+        <v>355.5300601438406</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29655,28 +29725,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5445768902584682</v>
+        <v>0.5382344808469591</v>
       </c>
       <c r="J3" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3556801907149911</v>
+        <v>0.3486190186427246</v>
       </c>
       <c r="M3" t="n">
-        <v>4.189014909760033</v>
+        <v>4.212033668877073</v>
       </c>
       <c r="N3" t="n">
-        <v>29.12192116863999</v>
+        <v>29.43600230813885</v>
       </c>
       <c r="O3" t="n">
-        <v>5.396473030474626</v>
+        <v>5.425495581800694</v>
       </c>
       <c r="P3" t="n">
-        <v>356.1846370567357</v>
+        <v>356.250287130699</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29733,28 +29803,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3496770095887513</v>
+        <v>0.3464557020179275</v>
       </c>
       <c r="J4" t="n">
+        <v>410</v>
+      </c>
+      <c r="K4" t="n">
         <v>409</v>
       </c>
-      <c r="K4" t="n">
-        <v>408</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2347502036358881</v>
+        <v>0.2316311014027812</v>
       </c>
       <c r="M4" t="n">
-        <v>3.492920177998569</v>
+        <v>3.498865040920412</v>
       </c>
       <c r="N4" t="n">
-        <v>21.56432785304157</v>
+        <v>21.61074790154097</v>
       </c>
       <c r="O4" t="n">
-        <v>4.643740717680259</v>
+        <v>4.648736161747725</v>
       </c>
       <c r="P4" t="n">
-        <v>368.1207966904065</v>
+        <v>368.1541562879882</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29811,28 +29881,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4353066530097467</v>
+        <v>0.4319333556172578</v>
       </c>
       <c r="J5" t="n">
+        <v>410</v>
+      </c>
+      <c r="K5" t="n">
         <v>409</v>
       </c>
-      <c r="K5" t="n">
-        <v>408</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2901677809364757</v>
+        <v>0.2872454471463719</v>
       </c>
       <c r="M5" t="n">
-        <v>3.690372329346591</v>
+        <v>3.69501729787732</v>
       </c>
       <c r="N5" t="n">
-        <v>25.07850544126538</v>
+        <v>25.12590989077287</v>
       </c>
       <c r="O5" t="n">
-        <v>5.007844390680024</v>
+        <v>5.012575175573217</v>
       </c>
       <c r="P5" t="n">
-        <v>367.3884591514413</v>
+        <v>367.4233927431779</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29889,28 +29959,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4118302345383447</v>
+        <v>0.4105996440871694</v>
       </c>
       <c r="J6" t="n">
+        <v>410</v>
+      </c>
+      <c r="K6" t="n">
         <v>409</v>
       </c>
-      <c r="K6" t="n">
-        <v>408</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3364332378898818</v>
+        <v>0.336182868680188</v>
       </c>
       <c r="M6" t="n">
-        <v>3.216898330803635</v>
+        <v>3.214444868841204</v>
       </c>
       <c r="N6" t="n">
-        <v>18.09783837435262</v>
+        <v>18.06805815077837</v>
       </c>
       <c r="O6" t="n">
-        <v>4.25415542432956</v>
+        <v>4.250653849795155</v>
       </c>
       <c r="P6" t="n">
-        <v>367.4191387198302</v>
+        <v>367.4318826138349</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29967,28 +30037,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4552399933173514</v>
+        <v>0.4544664118768542</v>
       </c>
       <c r="J7" t="n">
+        <v>410</v>
+      </c>
+      <c r="K7" t="n">
         <v>409</v>
       </c>
-      <c r="K7" t="n">
-        <v>408</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.3676104605013079</v>
+        <v>0.3680676177048486</v>
       </c>
       <c r="M7" t="n">
-        <v>3.165653778792467</v>
+        <v>3.161216975158567</v>
       </c>
       <c r="N7" t="n">
-        <v>19.28777607211645</v>
+        <v>19.24633533287972</v>
       </c>
       <c r="O7" t="n">
-        <v>4.391785066703112</v>
+        <v>4.387064546240427</v>
       </c>
       <c r="P7" t="n">
-        <v>366.2363402638139</v>
+        <v>366.2443514099041</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30045,28 +30115,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3879284631735515</v>
+        <v>0.3896410300255665</v>
       </c>
       <c r="J8" t="n">
+        <v>410</v>
+      </c>
+      <c r="K8" t="n">
         <v>409</v>
       </c>
-      <c r="K8" t="n">
-        <v>408</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3225517788161303</v>
+        <v>0.3253623051925157</v>
       </c>
       <c r="M8" t="n">
-        <v>3.284709208190252</v>
+        <v>3.285545062514594</v>
       </c>
       <c r="N8" t="n">
-        <v>17.0995420444699</v>
+        <v>17.08575590354761</v>
       </c>
       <c r="O8" t="n">
-        <v>4.135159252612878</v>
+        <v>4.133491974535285</v>
       </c>
       <c r="P8" t="n">
-        <v>364.8682785613168</v>
+        <v>364.8505433591484</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30123,28 +30193,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.321335838476042</v>
+        <v>0.3240576425591197</v>
       </c>
       <c r="J9" t="n">
+        <v>410</v>
+      </c>
+      <c r="K9" t="n">
         <v>409</v>
       </c>
-      <c r="K9" t="n">
-        <v>408</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.2014864931261399</v>
+        <v>0.2046150842948952</v>
       </c>
       <c r="M9" t="n">
-        <v>3.673671956575456</v>
+        <v>3.67935105282967</v>
       </c>
       <c r="N9" t="n">
-        <v>22.13906017064682</v>
+        <v>22.1557116934129</v>
       </c>
       <c r="O9" t="n">
-        <v>4.705216272462597</v>
+        <v>4.706985414616547</v>
       </c>
       <c r="P9" t="n">
-        <v>366.4106752436156</v>
+        <v>366.3824884632751</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30201,28 +30271,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2680631286284746</v>
+        <v>0.2705399840530922</v>
       </c>
       <c r="J10" t="n">
+        <v>410</v>
+      </c>
+      <c r="K10" t="n">
         <v>409</v>
       </c>
-      <c r="K10" t="n">
-        <v>408</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1837560424263601</v>
+        <v>0.1868754814793451</v>
       </c>
       <c r="M10" t="n">
-        <v>3.322174253034818</v>
+        <v>3.326889753518286</v>
       </c>
       <c r="N10" t="n">
-        <v>17.26859629324926</v>
+        <v>17.28498939189552</v>
       </c>
       <c r="O10" t="n">
-        <v>4.155550059047449</v>
+        <v>4.157522025425184</v>
       </c>
       <c r="P10" t="n">
-        <v>367.958879498222</v>
+        <v>367.9332293861427</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30279,28 +30349,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2366413796121759</v>
+        <v>0.239547383204996</v>
       </c>
       <c r="J11" t="n">
+        <v>410</v>
+      </c>
+      <c r="K11" t="n">
         <v>409</v>
       </c>
-      <c r="K11" t="n">
-        <v>408</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1394105725799842</v>
+        <v>0.1425299173615351</v>
       </c>
       <c r="M11" t="n">
-        <v>3.500170732500401</v>
+        <v>3.506900288234827</v>
       </c>
       <c r="N11" t="n">
-        <v>18.70191999022286</v>
+        <v>18.73687977170172</v>
       </c>
       <c r="O11" t="n">
-        <v>4.324571653958674</v>
+        <v>4.328611760333989</v>
       </c>
       <c r="P11" t="n">
-        <v>367.8143994852224</v>
+        <v>367.7843051498333</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30357,28 +30427,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2170310861334483</v>
+        <v>0.2195637756281823</v>
       </c>
       <c r="J12" t="n">
+        <v>410</v>
+      </c>
+      <c r="K12" t="n">
         <v>409</v>
       </c>
-      <c r="K12" t="n">
-        <v>408</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.0905161722644362</v>
+        <v>0.09271919974877596</v>
       </c>
       <c r="M12" t="n">
-        <v>4.270410418126224</v>
+        <v>4.270752142843779</v>
       </c>
       <c r="N12" t="n">
-        <v>25.60455370845554</v>
+        <v>25.60323789701242</v>
       </c>
       <c r="O12" t="n">
-        <v>5.060094239088392</v>
+        <v>5.059964218945863</v>
       </c>
       <c r="P12" t="n">
-        <v>362.9232737822746</v>
+        <v>362.8970454571345</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30435,28 +30505,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2303949101707662</v>
+        <v>0.2337939513423633</v>
       </c>
       <c r="J13" t="n">
+        <v>410</v>
+      </c>
+      <c r="K13" t="n">
         <v>409</v>
       </c>
-      <c r="K13" t="n">
-        <v>408</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.09542331914595104</v>
+        <v>0.09812396802009327</v>
       </c>
       <c r="M13" t="n">
-        <v>4.409000962126948</v>
+        <v>4.413713685306061</v>
       </c>
       <c r="N13" t="n">
-        <v>27.22332401809041</v>
+        <v>27.2671501841503</v>
       </c>
       <c r="O13" t="n">
-        <v>5.217597533165088</v>
+        <v>5.221795685791459</v>
       </c>
       <c r="P13" t="n">
-        <v>358.2686610322614</v>
+        <v>358.2334608400552</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30513,28 +30583,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1692687815255825</v>
+        <v>0.171689763060638</v>
       </c>
       <c r="J14" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K14" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0481006877477903</v>
+        <v>0.04959717925128115</v>
       </c>
       <c r="M14" t="n">
-        <v>4.732603368535835</v>
+        <v>4.731391402334578</v>
       </c>
       <c r="N14" t="n">
-        <v>30.91968146868032</v>
+        <v>30.90092343793096</v>
       </c>
       <c r="O14" t="n">
-        <v>5.560546867771219</v>
+        <v>5.558859904506585</v>
       </c>
       <c r="P14" t="n">
-        <v>352.4153494366698</v>
+        <v>352.3904217787796</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30591,28 +30661,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2658156208711207</v>
+        <v>0.2698969520477181</v>
       </c>
       <c r="J15" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K15" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09077778713841911</v>
+        <v>0.09344907427443261</v>
       </c>
       <c r="M15" t="n">
-        <v>5.294100314764722</v>
+        <v>5.297239605190065</v>
       </c>
       <c r="N15" t="n">
-        <v>38.59161839163628</v>
+        <v>38.6585071083919</v>
       </c>
       <c r="O15" t="n">
-        <v>6.212215256382885</v>
+        <v>6.217596570089756</v>
       </c>
       <c r="P15" t="n">
-        <v>350.3264234833567</v>
+        <v>350.2844000206273</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30669,28 +30739,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2431507652079896</v>
+        <v>0.2485344996135778</v>
       </c>
       <c r="J16" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K16" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06041513479758365</v>
+        <v>0.06295323863782121</v>
       </c>
       <c r="M16" t="n">
-        <v>5.842078784581035</v>
+        <v>5.848439687918409</v>
       </c>
       <c r="N16" t="n">
-        <v>50.13985726410161</v>
+        <v>50.29773960562042</v>
       </c>
       <c r="O16" t="n">
-        <v>7.08095030798138</v>
+        <v>7.092089932144151</v>
       </c>
       <c r="P16" t="n">
-        <v>353.0733160156602</v>
+        <v>353.0178823465095</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30747,28 +30817,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1813086437486558</v>
+        <v>0.1884599331572318</v>
       </c>
       <c r="J17" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K17" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02666828068416005</v>
+        <v>0.0286987474351017</v>
       </c>
       <c r="M17" t="n">
-        <v>6.695808955366645</v>
+        <v>6.707975198179233</v>
       </c>
       <c r="N17" t="n">
-        <v>65.42510462998048</v>
+        <v>65.75987641742286</v>
       </c>
       <c r="O17" t="n">
-        <v>8.088578653260441</v>
+        <v>8.10924635323301</v>
       </c>
       <c r="P17" t="n">
-        <v>352.7879445669726</v>
+        <v>352.7143112520259</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30806,7 +30876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R410"/>
+  <dimension ref="A1:R411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68473,6 +68543,98 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-36.83577377145319,175.80221293122293</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-36.83613129207356,175.80299264183765</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-36.836421817364645,175.80382401009888</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-36.836802455706085,175.80458589077423</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-36.837165331588274,175.80536434031</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-36.83756641306028,175.80611357831123</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-36.83796527100522,175.80686182191744</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-36.83836240693649,175.80760646048822</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-36.838757123805365,175.8083498401896</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-36.839137295028166,175.80910914857498</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-36.839565576186736,175.80983703976824</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>-36.83997447413958,175.81057849884346</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-36.840435366163256,175.8112797541163</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-36.840843042501824,175.81202064031143</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>-36.84126805137805,175.81274414830128</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>-36.841688385619626,175.81346931608275</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R411"/>
+  <dimension ref="A1:R413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25095,6 +25095,126 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>356.15</v>
+      </c>
+      <c r="C412" t="n">
+        <v>359.81</v>
+      </c>
+      <c r="D412" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="E412" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="F412" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="G412" t="n">
+        <v>377</v>
+      </c>
+      <c r="H412" t="n">
+        <v>378.56</v>
+      </c>
+      <c r="I412" t="n">
+        <v>380.17</v>
+      </c>
+      <c r="J412" t="n">
+        <v>379.84</v>
+      </c>
+      <c r="K412" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="L412" t="n">
+        <v>373.18</v>
+      </c>
+      <c r="M412" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="N412" t="n">
+        <v>361.01</v>
+      </c>
+      <c r="O412" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="P412" t="n">
+        <v>369.81</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>356.15</v>
+      </c>
+      <c r="C413" t="n">
+        <v>359.81</v>
+      </c>
+      <c r="D413" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="E413" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="F413" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="G413" t="n">
+        <v>377.95</v>
+      </c>
+      <c r="H413" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="I413" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>380.24</v>
+      </c>
+      <c r="K413" t="n">
+        <v>379.13</v>
+      </c>
+      <c r="L413" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="M413" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="N413" t="n">
+        <v>362.05</v>
+      </c>
+      <c r="O413" t="n">
+        <v>365.28</v>
+      </c>
+      <c r="P413" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>371.02</v>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25106,7 +25226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B437"/>
+  <dimension ref="A1:B439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29479,6 +29599,26 @@
       </c>
       <c r="B437" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -29647,28 +29787,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.350139107294283</v>
+        <v>0.3415341087610116</v>
       </c>
       <c r="J2" t="n">
+        <v>412</v>
+      </c>
+      <c r="K2" t="n">
         <v>410</v>
       </c>
-      <c r="K2" t="n">
-        <v>408</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1748253345102537</v>
+        <v>0.1677446450572323</v>
       </c>
       <c r="M2" t="n">
-        <v>4.275120533052866</v>
+        <v>4.30014263116977</v>
       </c>
       <c r="N2" t="n">
-        <v>31.46839228503618</v>
+        <v>31.67307051726162</v>
       </c>
       <c r="O2" t="n">
-        <v>5.609669534387582</v>
+        <v>5.627883307004653</v>
       </c>
       <c r="P2" t="n">
-        <v>355.5300601438406</v>
+        <v>355.619334371801</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29725,28 +29865,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5382344808469591</v>
+        <v>0.5275964701491785</v>
       </c>
       <c r="J3" t="n">
+        <v>412</v>
+      </c>
+      <c r="K3" t="n">
         <v>410</v>
       </c>
-      <c r="K3" t="n">
-        <v>408</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3486190186427246</v>
+        <v>0.3379807779698902</v>
       </c>
       <c r="M3" t="n">
-        <v>4.212033668877073</v>
+        <v>4.248385982698298</v>
       </c>
       <c r="N3" t="n">
-        <v>29.43600230813885</v>
+        <v>29.83983584017642</v>
       </c>
       <c r="O3" t="n">
-        <v>5.425495581800694</v>
+        <v>5.462585087682975</v>
       </c>
       <c r="P3" t="n">
-        <v>356.250287130699</v>
+        <v>356.3606532435892</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29803,28 +29943,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3464557020179275</v>
+        <v>0.3407036189208523</v>
       </c>
       <c r="J4" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K4" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2316311014027812</v>
+        <v>0.2264019989377715</v>
       </c>
       <c r="M4" t="n">
-        <v>3.498865040920412</v>
+        <v>3.507449618624348</v>
       </c>
       <c r="N4" t="n">
-        <v>21.61074790154097</v>
+        <v>21.66517259356927</v>
       </c>
       <c r="O4" t="n">
-        <v>4.648736161747725</v>
+        <v>4.654586189294304</v>
       </c>
       <c r="P4" t="n">
-        <v>368.1541562879882</v>
+        <v>368.2138604100594</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29881,28 +30021,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4319333556172578</v>
+        <v>0.424128850464333</v>
       </c>
       <c r="J5" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K5" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2872454471463719</v>
+        <v>0.2797527543782327</v>
       </c>
       <c r="M5" t="n">
-        <v>3.69501729787732</v>
+        <v>3.708430939261974</v>
       </c>
       <c r="N5" t="n">
-        <v>25.12590989077287</v>
+        <v>25.29743238451482</v>
       </c>
       <c r="O5" t="n">
-        <v>5.012575175573217</v>
+        <v>5.029655294800511</v>
       </c>
       <c r="P5" t="n">
-        <v>367.4233927431779</v>
+        <v>367.5044001119941</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29959,28 +30099,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4105996440871694</v>
+        <v>0.4089444125602372</v>
       </c>
       <c r="J6" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K6" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L6" t="n">
-        <v>0.336182868680188</v>
+        <v>0.3367292986399346</v>
       </c>
       <c r="M6" t="n">
-        <v>3.214444868841204</v>
+        <v>3.206059987178942</v>
       </c>
       <c r="N6" t="n">
-        <v>18.06805815077837</v>
+        <v>17.99335064790634</v>
       </c>
       <c r="O6" t="n">
-        <v>4.250653849795155</v>
+        <v>4.241856981076371</v>
       </c>
       <c r="P6" t="n">
-        <v>367.4318826138349</v>
+        <v>367.4490632137658</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30037,28 +30177,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4544664118768542</v>
+        <v>0.4536791647711338</v>
       </c>
       <c r="J7" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3680676177048486</v>
+        <v>0.369832813051912</v>
       </c>
       <c r="M7" t="n">
-        <v>3.161216975158567</v>
+        <v>3.149264784367173</v>
       </c>
       <c r="N7" t="n">
-        <v>19.24633533287972</v>
+        <v>19.15673943583337</v>
       </c>
       <c r="O7" t="n">
-        <v>4.387064546240427</v>
+        <v>4.376841262352722</v>
       </c>
       <c r="P7" t="n">
-        <v>366.2443514099041</v>
+        <v>366.2525204584818</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30115,28 +30255,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3896410300255665</v>
+        <v>0.3932100337346203</v>
       </c>
       <c r="J8" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K8" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3253623051925157</v>
+        <v>0.3310689155323585</v>
       </c>
       <c r="M8" t="n">
-        <v>3.285545062514594</v>
+        <v>3.28792427665207</v>
       </c>
       <c r="N8" t="n">
-        <v>17.08575590354761</v>
+        <v>17.06419212563277</v>
       </c>
       <c r="O8" t="n">
-        <v>4.133491974535285</v>
+        <v>4.130882729590949</v>
       </c>
       <c r="P8" t="n">
-        <v>364.8505433591484</v>
+        <v>364.8134978378986</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30193,28 +30333,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3240576425591197</v>
+        <v>0.3294185014909697</v>
       </c>
       <c r="J9" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K9" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2046150842948952</v>
+        <v>0.2108362671457406</v>
       </c>
       <c r="M9" t="n">
-        <v>3.67935105282967</v>
+        <v>3.690095745619991</v>
       </c>
       <c r="N9" t="n">
-        <v>22.1557116934129</v>
+        <v>22.18663059803229</v>
       </c>
       <c r="O9" t="n">
-        <v>4.706985414616547</v>
+        <v>4.710268633319366</v>
       </c>
       <c r="P9" t="n">
-        <v>366.3824884632751</v>
+        <v>366.3268443334591</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30271,28 +30411,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2705399840530922</v>
+        <v>0.2754726212801061</v>
       </c>
       <c r="J10" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K10" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1868754814793451</v>
+        <v>0.1931214113398607</v>
       </c>
       <c r="M10" t="n">
-        <v>3.326889753518286</v>
+        <v>3.336024206633127</v>
       </c>
       <c r="N10" t="n">
-        <v>17.28498939189552</v>
+        <v>17.31841832436621</v>
       </c>
       <c r="O10" t="n">
-        <v>4.157522025425184</v>
+        <v>4.161540378798001</v>
       </c>
       <c r="P10" t="n">
-        <v>367.9332293861427</v>
+        <v>367.8820298191184</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30349,28 +30489,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.239547383204996</v>
+        <v>0.2443836045038029</v>
       </c>
       <c r="J11" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K11" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1425299173615351</v>
+        <v>0.1481436186067948</v>
       </c>
       <c r="M11" t="n">
-        <v>3.506900288234827</v>
+        <v>3.51530390181795</v>
       </c>
       <c r="N11" t="n">
-        <v>18.73687977170172</v>
+        <v>18.75863109168656</v>
       </c>
       <c r="O11" t="n">
-        <v>4.328611760333989</v>
+        <v>4.33112353687661</v>
       </c>
       <c r="P11" t="n">
-        <v>367.7843051498333</v>
+        <v>367.7341065332609</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30427,28 +30567,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2195637756281823</v>
+        <v>0.2242110841710897</v>
       </c>
       <c r="J12" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K12" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09271919974877596</v>
+        <v>0.09692998411492493</v>
       </c>
       <c r="M12" t="n">
-        <v>4.270752142843779</v>
+        <v>4.269652647376833</v>
       </c>
       <c r="N12" t="n">
-        <v>25.60323789701242</v>
+        <v>25.58297325112845</v>
       </c>
       <c r="O12" t="n">
-        <v>5.059964218945863</v>
+        <v>5.057961373036418</v>
       </c>
       <c r="P12" t="n">
-        <v>362.8970454571345</v>
+        <v>362.8488075603686</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30505,28 +30645,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2337939513423633</v>
+        <v>0.2399238688584775</v>
       </c>
       <c r="J13" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09812396802009327</v>
+        <v>0.1032255224431655</v>
       </c>
       <c r="M13" t="n">
-        <v>4.413713685306061</v>
+        <v>4.419896094791888</v>
       </c>
       <c r="N13" t="n">
-        <v>27.2671501841503</v>
+        <v>27.31597080989008</v>
       </c>
       <c r="O13" t="n">
-        <v>5.221795685791459</v>
+        <v>5.226468292249565</v>
       </c>
       <c r="P13" t="n">
-        <v>358.2334608400552</v>
+        <v>358.1698338353459</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30583,28 +30723,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.171689763060638</v>
+        <v>0.1762375861308164</v>
       </c>
       <c r="J14" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K14" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04959717925128115</v>
+        <v>0.0525124633067604</v>
       </c>
       <c r="M14" t="n">
-        <v>4.731391402334578</v>
+        <v>4.727806012518847</v>
       </c>
       <c r="N14" t="n">
-        <v>30.90092343793096</v>
+        <v>30.85312947273517</v>
       </c>
       <c r="O14" t="n">
-        <v>5.558859904506585</v>
+        <v>5.554559341004034</v>
       </c>
       <c r="P14" t="n">
-        <v>352.3904217787796</v>
+        <v>352.343484950181</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30661,28 +30801,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2698969520477181</v>
+        <v>0.2774413329093202</v>
       </c>
       <c r="J15" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K15" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09344907427443261</v>
+        <v>0.09858270140417691</v>
       </c>
       <c r="M15" t="n">
-        <v>5.297239605190065</v>
+        <v>5.300933028986965</v>
       </c>
       <c r="N15" t="n">
-        <v>38.6585071083919</v>
+        <v>38.74882459580372</v>
       </c>
       <c r="O15" t="n">
-        <v>6.217596570089756</v>
+        <v>6.224855387541442</v>
       </c>
       <c r="P15" t="n">
-        <v>350.2844000206273</v>
+        <v>350.2065395312655</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30739,28 +30879,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2485344996135778</v>
+        <v>0.2589941107658907</v>
       </c>
       <c r="J16" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K16" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06295323863782121</v>
+        <v>0.0680336204642833</v>
       </c>
       <c r="M16" t="n">
-        <v>5.848439687918409</v>
+        <v>5.859914915627429</v>
       </c>
       <c r="N16" t="n">
-        <v>50.29773960562042</v>
+        <v>50.58799599678347</v>
       </c>
       <c r="O16" t="n">
-        <v>7.092089932144151</v>
+        <v>7.112523883740811</v>
       </c>
       <c r="P16" t="n">
-        <v>353.0178823465095</v>
+        <v>352.9099355660743</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30817,28 +30957,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1884599331572318</v>
+        <v>0.2012029426892359</v>
       </c>
       <c r="J17" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K17" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0286987474351017</v>
+        <v>0.03255411746875658</v>
       </c>
       <c r="M17" t="n">
-        <v>6.707975198179233</v>
+        <v>6.725661277166693</v>
       </c>
       <c r="N17" t="n">
-        <v>65.75987641742286</v>
+        <v>66.23391797980874</v>
       </c>
       <c r="O17" t="n">
-        <v>8.10924635323301</v>
+        <v>8.138422327442139</v>
       </c>
       <c r="P17" t="n">
-        <v>352.7143112520259</v>
+        <v>352.5827989692822</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30876,7 +31016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R411"/>
+  <dimension ref="A1:R413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68635,6 +68775,190 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-36.83575524317481,175.8022272184598</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-36.83611720441484,175.80300350480894</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-36.83641737667511,175.8038274342744</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-36.83681141367447,175.8045789834137</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-36.83715941057841,175.8053690459993</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-36.83756431283695,175.80611531576707</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-36.83796489714638,175.80686213437698</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-36.8383633127786,175.8076057267237</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-36.8387579680967,175.808349194981</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-36.8391451806601,175.80910328220298</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-36.839569425662646,175.80983413099145</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>-36.839980377154006,175.81057396813543</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>-36.84044067286206,175.81127531320516</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-36.840847979688135,175.81201594303417</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>-36.84127120330218,175.81274115874598</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>-36.8417010635914,175.8134578505799</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-36.83575524317481,175.8022272184598</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-36.83611720441484,175.80300350480894</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-36.83641737667511,175.8038274342744</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-36.83681141367447,175.8045789834137</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-36.83715941057841,175.8053690459993</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-36.837557187079064,175.8061212107059</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-36.83796228013444,175.80686432159368</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-36.8383608217128,175.8076077445761</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-36.83875489794635,175.80835154119413</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-36.83914270673639,175.80910512263355</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-36.83956657705048,175.8098362834863</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-36.839976697352824,175.81057679247297</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-36.840432899669395,175.81128181820154</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-36.84084461667718,175.81201914262888</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-36.84126611724275,175.812745982801</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-36.84169457888182,175.81346371511918</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R413"/>
+  <dimension ref="A1:R415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25215,6 +25215,126 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>358.95</v>
+      </c>
+      <c r="C414" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="D414" t="n">
+        <v>372.35</v>
+      </c>
+      <c r="E414" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="F414" t="n">
+        <v>376.28</v>
+      </c>
+      <c r="G414" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="H414" t="n">
+        <v>378.27</v>
+      </c>
+      <c r="I414" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="J414" t="n">
+        <v>379.33</v>
+      </c>
+      <c r="K414" t="n">
+        <v>378.46</v>
+      </c>
+      <c r="L414" t="n">
+        <v>373.33</v>
+      </c>
+      <c r="M414" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="N414" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="O414" t="n">
+        <v>364.61</v>
+      </c>
+      <c r="P414" t="n">
+        <v>370.05</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>369.74</v>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>359.92</v>
+      </c>
+      <c r="C415" t="n">
+        <v>361</v>
+      </c>
+      <c r="D415" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="E415" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="F415" t="n">
+        <v>375.63</v>
+      </c>
+      <c r="G415" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="H415" t="n">
+        <v>376.93</v>
+      </c>
+      <c r="I415" t="n">
+        <v>377.64</v>
+      </c>
+      <c r="J415" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="K415" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="L415" t="n">
+        <v>374.03</v>
+      </c>
+      <c r="M415" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="N415" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="O415" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="P415" t="n">
+        <v>368.73</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>368.19</v>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25226,7 +25346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B439"/>
+  <dimension ref="A1:B441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29619,6 +29739,26 @@
       </c>
       <c r="B439" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -29787,28 +29927,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3415341087610116</v>
+        <v>0.3363746080124989</v>
       </c>
       <c r="J2" t="n">
+        <v>414</v>
+      </c>
+      <c r="K2" t="n">
         <v>412</v>
       </c>
-      <c r="K2" t="n">
-        <v>410</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1677446450572323</v>
+        <v>0.1644889021997433</v>
       </c>
       <c r="M2" t="n">
-        <v>4.30014263116977</v>
+        <v>4.307189906794364</v>
       </c>
       <c r="N2" t="n">
-        <v>31.67307051726162</v>
+        <v>31.65151131681181</v>
       </c>
       <c r="O2" t="n">
-        <v>5.627883307004653</v>
+        <v>5.625967589385119</v>
       </c>
       <c r="P2" t="n">
-        <v>355.619334371801</v>
+        <v>355.6729812554065</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29865,28 +30005,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5275964701491785</v>
+        <v>0.5187665789580739</v>
       </c>
       <c r="J3" t="n">
+        <v>414</v>
+      </c>
+      <c r="K3" t="n">
         <v>412</v>
       </c>
-      <c r="K3" t="n">
-        <v>410</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3379807779698902</v>
+        <v>0.3300850863481737</v>
       </c>
       <c r="M3" t="n">
-        <v>4.248385982698298</v>
+        <v>4.275332447566633</v>
       </c>
       <c r="N3" t="n">
-        <v>29.83983584017642</v>
+        <v>30.07946750613655</v>
       </c>
       <c r="O3" t="n">
-        <v>5.462585087682975</v>
+        <v>5.484475134972949</v>
       </c>
       <c r="P3" t="n">
-        <v>356.3606532435892</v>
+        <v>356.4524751991186</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29943,28 +30083,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3407036189208523</v>
+        <v>0.3359452897783812</v>
       </c>
       <c r="J4" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K4" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2264019989377715</v>
+        <v>0.2225485855120759</v>
       </c>
       <c r="M4" t="n">
-        <v>3.507449618624348</v>
+        <v>3.511536440099998</v>
       </c>
       <c r="N4" t="n">
-        <v>21.66517259356927</v>
+        <v>21.67141312971747</v>
       </c>
       <c r="O4" t="n">
-        <v>4.654586189294304</v>
+        <v>4.655256505254836</v>
       </c>
       <c r="P4" t="n">
-        <v>368.2138604100594</v>
+        <v>368.2633624853749</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30021,28 +30161,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.424128850464333</v>
+        <v>0.4154323653722524</v>
       </c>
       <c r="J5" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K5" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2797527543782327</v>
+        <v>0.270781215442305</v>
       </c>
       <c r="M5" t="n">
-        <v>3.708430939261974</v>
+        <v>3.725759308986792</v>
       </c>
       <c r="N5" t="n">
-        <v>25.29743238451482</v>
+        <v>25.5471036442059</v>
       </c>
       <c r="O5" t="n">
-        <v>5.029655294800511</v>
+        <v>5.054414273108795</v>
       </c>
       <c r="P5" t="n">
-        <v>367.5044001119941</v>
+        <v>367.5948771233495</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30099,28 +30239,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4089444125602372</v>
+        <v>0.4066474925373663</v>
       </c>
       <c r="J6" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K6" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3367292986399346</v>
+        <v>0.3363712735691422</v>
       </c>
       <c r="M6" t="n">
-        <v>3.206059987178942</v>
+        <v>3.200499292523094</v>
       </c>
       <c r="N6" t="n">
-        <v>17.99335064790634</v>
+        <v>17.93263767924752</v>
       </c>
       <c r="O6" t="n">
-        <v>4.241856981076371</v>
+        <v>4.23469452018059</v>
       </c>
       <c r="P6" t="n">
-        <v>367.4490632137658</v>
+        <v>367.4729620600451</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30177,28 +30317,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4536791647711338</v>
+        <v>0.4523830932469473</v>
       </c>
       <c r="J7" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K7" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L7" t="n">
-        <v>0.369832813051912</v>
+        <v>0.3709880581596462</v>
       </c>
       <c r="M7" t="n">
-        <v>3.149264784367173</v>
+        <v>3.139630845712493</v>
       </c>
       <c r="N7" t="n">
-        <v>19.15673943583337</v>
+        <v>19.0727532860231</v>
       </c>
       <c r="O7" t="n">
-        <v>4.376841262352722</v>
+        <v>4.367236344191038</v>
       </c>
       <c r="P7" t="n">
-        <v>366.2525204584818</v>
+        <v>366.2660071364937</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30255,28 +30395,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3932100337346203</v>
+        <v>0.3955423951533045</v>
       </c>
       <c r="J8" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K8" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3310689155323585</v>
+        <v>0.3357941614473943</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28792427665207</v>
+        <v>3.283912088320232</v>
       </c>
       <c r="N8" t="n">
-        <v>17.06419212563277</v>
+        <v>17.01050963166625</v>
       </c>
       <c r="O8" t="n">
-        <v>4.130882729590949</v>
+        <v>4.124379908745828</v>
       </c>
       <c r="P8" t="n">
-        <v>364.8134978378986</v>
+        <v>364.7892398711965</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30333,28 +30473,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3294185014909697</v>
+        <v>0.3329026093066724</v>
       </c>
       <c r="J9" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K9" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2108362671457406</v>
+        <v>0.2157487499099627</v>
       </c>
       <c r="M9" t="n">
-        <v>3.690095745619991</v>
+        <v>3.691024410765636</v>
       </c>
       <c r="N9" t="n">
-        <v>22.18663059803229</v>
+        <v>22.14333492641378</v>
       </c>
       <c r="O9" t="n">
-        <v>4.710268633319366</v>
+        <v>4.705670507633719</v>
       </c>
       <c r="P9" t="n">
-        <v>366.3268443334591</v>
+        <v>366.2906070543221</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30411,28 +30551,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2754726212801061</v>
+        <v>0.2791162871369315</v>
       </c>
       <c r="J10" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K10" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1931214113398607</v>
+        <v>0.1984083548148334</v>
       </c>
       <c r="M10" t="n">
-        <v>3.336024206633127</v>
+        <v>3.338402525746364</v>
       </c>
       <c r="N10" t="n">
-        <v>17.31841832436621</v>
+        <v>17.30076407217618</v>
       </c>
       <c r="O10" t="n">
-        <v>4.161540378798001</v>
+        <v>4.1594187180634</v>
       </c>
       <c r="P10" t="n">
-        <v>367.8820298191184</v>
+        <v>367.8441278003692</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30489,28 +30629,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2443836045038029</v>
+        <v>0.2479132686055009</v>
       </c>
       <c r="J11" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K11" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1481436186067948</v>
+        <v>0.1527998801498046</v>
       </c>
       <c r="M11" t="n">
-        <v>3.51530390181795</v>
+        <v>3.516796001474617</v>
       </c>
       <c r="N11" t="n">
-        <v>18.75863109168656</v>
+        <v>18.73114115152083</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33112353687661</v>
+        <v>4.327948838828948</v>
       </c>
       <c r="P11" t="n">
-        <v>367.7341065332609</v>
+        <v>367.6973925005408</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30567,28 +30707,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2242110841710897</v>
+        <v>0.2290285919948629</v>
       </c>
       <c r="J12" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K12" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09692998411492493</v>
+        <v>0.1013200388611551</v>
       </c>
       <c r="M12" t="n">
-        <v>4.269652647376833</v>
+        <v>4.269392583521373</v>
       </c>
       <c r="N12" t="n">
-        <v>25.58297325112845</v>
+        <v>25.5735380190255</v>
       </c>
       <c r="O12" t="n">
-        <v>5.057961373036418</v>
+        <v>5.057028576053876</v>
       </c>
       <c r="P12" t="n">
-        <v>362.8488075603686</v>
+        <v>362.7986860631642</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30645,28 +30785,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2399238688584775</v>
+        <v>0.2444740036948082</v>
       </c>
       <c r="J13" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K13" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1032255224431655</v>
+        <v>0.1074604268942332</v>
       </c>
       <c r="M13" t="n">
-        <v>4.419896094791888</v>
+        <v>4.418895738685188</v>
       </c>
       <c r="N13" t="n">
-        <v>27.31597080989008</v>
+        <v>27.28638409221494</v>
       </c>
       <c r="O13" t="n">
-        <v>5.226468292249565</v>
+        <v>5.223637055942434</v>
       </c>
       <c r="P13" t="n">
-        <v>358.1698338353459</v>
+        <v>358.1225015302102</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30723,28 +30863,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1762375861308164</v>
+        <v>0.1815144004554521</v>
       </c>
       <c r="J14" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K14" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0525124633067604</v>
+        <v>0.05586715384430119</v>
       </c>
       <c r="M14" t="n">
-        <v>4.727806012518847</v>
+        <v>4.727315082105415</v>
       </c>
       <c r="N14" t="n">
-        <v>30.85312947273517</v>
+        <v>30.84645091813137</v>
       </c>
       <c r="O14" t="n">
-        <v>5.554559341004034</v>
+        <v>5.55395813075066</v>
       </c>
       <c r="P14" t="n">
-        <v>352.343484950181</v>
+        <v>352.2888927435902</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30801,28 +30941,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2774413329093202</v>
+        <v>0.2852131027253559</v>
       </c>
       <c r="J15" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K15" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09858270140417691</v>
+        <v>0.1039054696518568</v>
       </c>
       <c r="M15" t="n">
-        <v>5.300933028986965</v>
+        <v>5.305444406517241</v>
       </c>
       <c r="N15" t="n">
-        <v>38.74882459580372</v>
+        <v>38.86519354760962</v>
       </c>
       <c r="O15" t="n">
-        <v>6.224855387541442</v>
+        <v>6.234195501234271</v>
       </c>
       <c r="P15" t="n">
-        <v>350.2065395312655</v>
+        <v>350.126139942141</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30879,28 +31019,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2589941107658907</v>
+        <v>0.2683991219751952</v>
       </c>
       <c r="J16" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K16" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0680336204642833</v>
+        <v>0.07285823083801501</v>
       </c>
       <c r="M16" t="n">
-        <v>5.859914915627429</v>
+        <v>5.86832297864638</v>
       </c>
       <c r="N16" t="n">
-        <v>50.58799599678347</v>
+        <v>50.78508445649289</v>
       </c>
       <c r="O16" t="n">
-        <v>7.112523883740811</v>
+        <v>7.126365445056329</v>
       </c>
       <c r="P16" t="n">
-        <v>352.9099355660743</v>
+        <v>352.8126563170406</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30957,28 +31097,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2012029426892359</v>
+        <v>0.2120145941335826</v>
       </c>
       <c r="J17" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K17" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03255411746875658</v>
+        <v>0.03609661509572692</v>
       </c>
       <c r="M17" t="n">
-        <v>6.725661277166693</v>
+        <v>6.735365725322529</v>
       </c>
       <c r="N17" t="n">
-        <v>66.23391797980874</v>
+        <v>66.49745316323079</v>
       </c>
       <c r="O17" t="n">
-        <v>8.138422327442139</v>
+        <v>8.154597057073438</v>
       </c>
       <c r="P17" t="n">
-        <v>352.5827989692822</v>
+        <v>352.4709704809939</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31016,7 +31156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R413"/>
+  <dimension ref="A1:R415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68959,6 +69099,190 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-36.83573380549552,175.8022437491387</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-36.83610227455822,175.80301501719276</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-36.83641117502234,175.80383221631203</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-36.8368163137596,175.80457520502782</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-36.837162067441824,175.80536693447212</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-36.83756213760563,175.80611711527484</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-36.83796706552765,175.8068603221116</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-36.83836799296275,175.8076019356067</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-36.83876188253834,175.80834620355895</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-36.83914788651413,175.80910126923195</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-36.839568270819875,175.80983500362453</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-36.83998597351818,175.8105696727882</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-36.840437234719204,175.81127819041527</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-36.8408494107566,175.8120145815044</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-36.84126948407085,175.81274278941254</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-36.84170390520564,175.8134552807253</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-36.83572637887044,175.80224947583608</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-36.83610809337426,175.80301053031545</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-36.83641017969534,175.80383298379948</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-36.83682320450413,175.80456989167186</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-36.83716700161668,175.80536301306418</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-36.83756701312409,175.80611308189526</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-36.83797708494434,175.80685194819438</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-36.83838241094877,175.80759025651767</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-36.83876879037638,175.80834092457823</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-36.8391581687592,175.80909361994065</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-36.83956288155357,175.8098390759118</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-36.839992949807566,175.81056431831348</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-36.84042325792038,175.8112898868972</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-36.840836674246766,175.81202669911747</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-36.84127893984294,175.81273382074548</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-36.84171519880016,175.81344506719876</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R415"/>
+  <dimension ref="A1:R416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25335,6 +25335,66 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="C416" t="n">
+        <v>360.95</v>
+      </c>
+      <c r="D416" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="E416" t="n">
+        <v>368.81</v>
+      </c>
+      <c r="F416" t="n">
+        <v>374.28</v>
+      </c>
+      <c r="G416" t="n">
+        <v>375.62</v>
+      </c>
+      <c r="H416" t="n">
+        <v>375.67</v>
+      </c>
+      <c r="I416" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="J416" t="n">
+        <v>377.12</v>
+      </c>
+      <c r="K416" t="n">
+        <v>376.57</v>
+      </c>
+      <c r="L416" t="n">
+        <v>372.96</v>
+      </c>
+      <c r="M416" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="N416" t="n">
+        <v>361.87</v>
+      </c>
+      <c r="O416" t="n">
+        <v>362.13</v>
+      </c>
+      <c r="P416" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>365.34</v>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25346,7 +25406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B441"/>
+  <dimension ref="A1:B442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29759,6 +29819,16 @@
       </c>
       <c r="B441" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -29927,28 +29997,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3363746080124989</v>
+        <v>0.3334419211375329</v>
       </c>
       <c r="J2" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K2" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1644889021997433</v>
+        <v>0.1625034761495099</v>
       </c>
       <c r="M2" t="n">
-        <v>4.307189906794364</v>
+        <v>4.312468500582569</v>
       </c>
       <c r="N2" t="n">
-        <v>31.65151131681181</v>
+        <v>31.65875104460243</v>
       </c>
       <c r="O2" t="n">
-        <v>5.625967589385119</v>
+        <v>5.626610973277113</v>
       </c>
       <c r="P2" t="n">
-        <v>355.6729812554065</v>
+        <v>355.7037000702675</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30005,28 +30075,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5187665789580739</v>
+        <v>0.5141297913845554</v>
       </c>
       <c r="J3" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K3" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3300850863481737</v>
+        <v>0.3258378161732413</v>
       </c>
       <c r="M3" t="n">
-        <v>4.275332447566633</v>
+        <v>4.289894815949134</v>
       </c>
       <c r="N3" t="n">
-        <v>30.07946750613655</v>
+        <v>30.2163124257214</v>
       </c>
       <c r="O3" t="n">
-        <v>5.484475134972949</v>
+        <v>5.496936640140706</v>
       </c>
       <c r="P3" t="n">
-        <v>356.4524751991186</v>
+        <v>356.5010438411502</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30083,28 +30153,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3359452897783812</v>
+        <v>0.3335336918244268</v>
       </c>
       <c r="J4" t="n">
+        <v>415</v>
+      </c>
+      <c r="K4" t="n">
         <v>414</v>
       </c>
-      <c r="K4" t="n">
-        <v>413</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2225485855120759</v>
+        <v>0.2205880744724878</v>
       </c>
       <c r="M4" t="n">
-        <v>3.511536440099998</v>
+        <v>3.513650649828684</v>
       </c>
       <c r="N4" t="n">
-        <v>21.67141312971747</v>
+        <v>21.67562383727034</v>
       </c>
       <c r="O4" t="n">
-        <v>4.655256505254836</v>
+        <v>4.655708736301095</v>
       </c>
       <c r="P4" t="n">
-        <v>368.2633624853749</v>
+        <v>368.2886340167255</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30161,28 +30231,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4154323653722524</v>
+        <v>0.4105364717461795</v>
       </c>
       <c r="J5" t="n">
+        <v>415</v>
+      </c>
+      <c r="K5" t="n">
         <v>414</v>
       </c>
-      <c r="K5" t="n">
-        <v>413</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.270781215442305</v>
+        <v>0.265451678264978</v>
       </c>
       <c r="M5" t="n">
-        <v>3.725759308986792</v>
+        <v>3.736341542460652</v>
       </c>
       <c r="N5" t="n">
-        <v>25.5471036442059</v>
+        <v>25.71849518971805</v>
       </c>
       <c r="O5" t="n">
-        <v>5.054414273108795</v>
+        <v>5.07134057126102</v>
       </c>
       <c r="P5" t="n">
-        <v>367.5948771233495</v>
+        <v>367.6461819973886</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30239,28 +30309,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4066474925373663</v>
+        <v>0.4046400583268948</v>
       </c>
       <c r="J6" t="n">
+        <v>415</v>
+      </c>
+      <c r="K6" t="n">
         <v>414</v>
       </c>
-      <c r="K6" t="n">
-        <v>413</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3363712735691422</v>
+        <v>0.3349371854473147</v>
       </c>
       <c r="M6" t="n">
-        <v>3.200499292523094</v>
+        <v>3.201425491608905</v>
       </c>
       <c r="N6" t="n">
-        <v>17.93263767924752</v>
+        <v>17.92851075962347</v>
       </c>
       <c r="O6" t="n">
-        <v>4.23469452018059</v>
+        <v>4.234207217369441</v>
       </c>
       <c r="P6" t="n">
-        <v>367.4729620600451</v>
+        <v>367.4939982930958</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30317,28 +30387,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4523830932469473</v>
+        <v>0.4510356837212244</v>
       </c>
       <c r="J7" t="n">
+        <v>415</v>
+      </c>
+      <c r="K7" t="n">
         <v>414</v>
       </c>
-      <c r="K7" t="n">
-        <v>413</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.3709880581596462</v>
+        <v>0.3706990385930161</v>
       </c>
       <c r="M7" t="n">
-        <v>3.139630845712493</v>
+        <v>3.137839594332362</v>
       </c>
       <c r="N7" t="n">
-        <v>19.0727532860231</v>
+        <v>19.04433919737744</v>
       </c>
       <c r="O7" t="n">
-        <v>4.367236344191038</v>
+        <v>4.363982034492974</v>
       </c>
       <c r="P7" t="n">
-        <v>366.2660071364937</v>
+        <v>366.2801268623856</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30395,28 +30465,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3955423951533045</v>
+        <v>0.3957055187735197</v>
       </c>
       <c r="J8" t="n">
+        <v>415</v>
+      </c>
+      <c r="K8" t="n">
         <v>414</v>
       </c>
-      <c r="K8" t="n">
-        <v>413</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3357941614473943</v>
+        <v>0.3372373920048011</v>
       </c>
       <c r="M8" t="n">
-        <v>3.283912088320232</v>
+        <v>3.276797956527447</v>
       </c>
       <c r="N8" t="n">
-        <v>17.01050963166625</v>
+        <v>16.96968021249328</v>
       </c>
       <c r="O8" t="n">
-        <v>4.124379908745828</v>
+        <v>4.119427170431986</v>
       </c>
       <c r="P8" t="n">
-        <v>364.7892398711965</v>
+        <v>364.7875304719678</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30473,28 +30543,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3329026093066724</v>
+        <v>0.3335874025544558</v>
       </c>
       <c r="J9" t="n">
+        <v>415</v>
+      </c>
+      <c r="K9" t="n">
         <v>414</v>
       </c>
-      <c r="K9" t="n">
-        <v>413</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.2157487499099627</v>
+        <v>0.2173703717756459</v>
       </c>
       <c r="M9" t="n">
-        <v>3.691024410765636</v>
+        <v>3.685739573906034</v>
       </c>
       <c r="N9" t="n">
-        <v>22.14333492641378</v>
+        <v>22.09440894133001</v>
       </c>
       <c r="O9" t="n">
-        <v>4.705670507633719</v>
+        <v>4.700469012910308</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2906070543221</v>
+        <v>366.2834309933201</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30551,28 +30621,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2791162871369315</v>
+        <v>0.2800251283380636</v>
       </c>
       <c r="J10" t="n">
+        <v>415</v>
+      </c>
+      <c r="K10" t="n">
         <v>414</v>
       </c>
-      <c r="K10" t="n">
-        <v>413</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1984083548148334</v>
+        <v>0.2002742757224347</v>
       </c>
       <c r="M10" t="n">
-        <v>3.338402525746364</v>
+        <v>3.334880062660649</v>
       </c>
       <c r="N10" t="n">
-        <v>17.30076407217618</v>
+        <v>17.26700733733009</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1594187180634</v>
+        <v>4.155358869860711</v>
       </c>
       <c r="P10" t="n">
-        <v>367.8441278003692</v>
+        <v>367.8346039040375</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30629,28 +30699,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2479132686055009</v>
+        <v>0.2490357524416136</v>
       </c>
       <c r="J11" t="n">
+        <v>415</v>
+      </c>
+      <c r="K11" t="n">
         <v>414</v>
       </c>
-      <c r="K11" t="n">
-        <v>413</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1527998801498046</v>
+        <v>0.1546254886072685</v>
       </c>
       <c r="M11" t="n">
-        <v>3.516796001474617</v>
+        <v>3.51408899005485</v>
       </c>
       <c r="N11" t="n">
-        <v>18.73114115152083</v>
+        <v>18.69814971382081</v>
       </c>
       <c r="O11" t="n">
-        <v>4.327948838828948</v>
+        <v>4.324135718709672</v>
       </c>
       <c r="P11" t="n">
-        <v>367.6973925005408</v>
+        <v>367.685629807921</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30707,28 +30777,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2290285919948629</v>
+        <v>0.2310390341376764</v>
       </c>
       <c r="J12" t="n">
+        <v>415</v>
+      </c>
+      <c r="K12" t="n">
         <v>414</v>
       </c>
-      <c r="K12" t="n">
-        <v>413</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1013200388611551</v>
+        <v>0.1033033283359729</v>
       </c>
       <c r="M12" t="n">
-        <v>4.269392583521373</v>
+        <v>4.267609152801437</v>
       </c>
       <c r="N12" t="n">
-        <v>25.5735380190255</v>
+        <v>25.55107234658445</v>
       </c>
       <c r="O12" t="n">
-        <v>5.057028576053876</v>
+        <v>5.054806855517277</v>
       </c>
       <c r="P12" t="n">
-        <v>362.7986860631642</v>
+        <v>362.7776183094959</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30785,28 +30855,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2444740036948082</v>
+        <v>0.2459454532111184</v>
       </c>
       <c r="J13" t="n">
+        <v>415</v>
+      </c>
+      <c r="K13" t="n">
         <v>414</v>
       </c>
-      <c r="K13" t="n">
-        <v>413</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1074604268942332</v>
+        <v>0.1090904813380589</v>
       </c>
       <c r="M13" t="n">
-        <v>4.418895738685188</v>
+        <v>4.414760452687626</v>
       </c>
       <c r="N13" t="n">
-        <v>27.28638409221494</v>
+        <v>27.24153057876423</v>
       </c>
       <c r="O13" t="n">
-        <v>5.223637055942434</v>
+        <v>5.219341967984492</v>
       </c>
       <c r="P13" t="n">
-        <v>358.1225015302102</v>
+        <v>358.1070819688686</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30863,28 +30933,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1815144004554521</v>
+        <v>0.1838508369193133</v>
       </c>
       <c r="J14" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K14" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05586715384430119</v>
+        <v>0.0574420414025566</v>
       </c>
       <c r="M14" t="n">
-        <v>4.727315082105415</v>
+        <v>4.725661256356049</v>
       </c>
       <c r="N14" t="n">
-        <v>30.84645091813137</v>
+        <v>30.8258267300553</v>
       </c>
       <c r="O14" t="n">
-        <v>5.55395813075066</v>
+        <v>5.552101109494973</v>
       </c>
       <c r="P14" t="n">
-        <v>352.2888927435902</v>
+        <v>352.2645472778996</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30941,28 +31011,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2852131027253559</v>
+        <v>0.2873788991600599</v>
       </c>
       <c r="J15" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K15" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1039054696518568</v>
+        <v>0.1057421529851963</v>
       </c>
       <c r="M15" t="n">
-        <v>5.305444406517241</v>
+        <v>5.300879722537394</v>
       </c>
       <c r="N15" t="n">
-        <v>38.86519354760962</v>
+        <v>38.81768899073598</v>
       </c>
       <c r="O15" t="n">
-        <v>6.234195501234271</v>
+        <v>6.230384337321092</v>
       </c>
       <c r="P15" t="n">
-        <v>350.126139942141</v>
+        <v>350.1035725307822</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31019,28 +31089,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2683991219751952</v>
+        <v>0.2715067864552312</v>
       </c>
       <c r="J16" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K16" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07285823083801501</v>
+        <v>0.07468830837232088</v>
       </c>
       <c r="M16" t="n">
-        <v>5.86832297864638</v>
+        <v>5.866174513693101</v>
       </c>
       <c r="N16" t="n">
-        <v>50.78508445649289</v>
+        <v>50.75772131476033</v>
       </c>
       <c r="O16" t="n">
-        <v>7.126365445056329</v>
+        <v>7.124445333831984</v>
       </c>
       <c r="P16" t="n">
-        <v>352.8126563170406</v>
+        <v>352.7802747221859</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31097,28 +31167,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2120145941335826</v>
+        <v>0.2155718715744487</v>
       </c>
       <c r="J17" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K17" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03609661509572692</v>
+        <v>0.03740764725253343</v>
       </c>
       <c r="M17" t="n">
-        <v>6.735365725322529</v>
+        <v>6.732732380019706</v>
       </c>
       <c r="N17" t="n">
-        <v>66.49745316323079</v>
+        <v>66.46170966068087</v>
       </c>
       <c r="O17" t="n">
-        <v>8.154597057073438</v>
+        <v>8.152405145764094</v>
       </c>
       <c r="P17" t="n">
-        <v>352.4709704809939</v>
+        <v>352.4339039580099</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31156,7 +31226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R415"/>
+  <dimension ref="A1:R416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69283,6 +69353,98 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-36.835735413321544,175.8022425093381</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-36.83610847619108,175.80301023512615</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-36.836411021895124,175.803832334387</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-36.836828257716654,175.80456599521023</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-36.83717724951793,175.8053548685999</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-36.837574663937424,175.8061067525909</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-36.83798650618642,175.80684407421055</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-36.83839063901364,175.8075835914859</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-36.838778845118036,175.8083332407268</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-36.839162498125404,175.80909039918583</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-36.83957111943202,175.80983285112958</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-36.84000122935955,175.810557963551</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-36.84043424502969,175.81128069233688</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-36.84086715600444,175.81199769853126</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-36.841296490327444,175.81271717435015</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-36.841735964439714,175.81342628748095</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R416"/>
+  <dimension ref="A1:R418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25395,6 +25395,126 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>358.62</v>
+      </c>
+      <c r="C417" t="n">
+        <v>361.1</v>
+      </c>
+      <c r="D417" t="n">
+        <v>372.34</v>
+      </c>
+      <c r="E417" t="n">
+        <v>369.28</v>
+      </c>
+      <c r="F417" t="n">
+        <v>374.07</v>
+      </c>
+      <c r="G417" t="n">
+        <v>375.42</v>
+      </c>
+      <c r="H417" t="n">
+        <v>375.07</v>
+      </c>
+      <c r="I417" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="J417" t="n">
+        <v>376.76</v>
+      </c>
+      <c r="K417" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="L417" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="M417" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="N417" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="O417" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="P417" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>360.57</v>
+      </c>
+      <c r="C418" t="n">
+        <v>362.59</v>
+      </c>
+      <c r="D418" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="E418" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="F418" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="G418" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="H418" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="I418" t="n">
+        <v>376.11</v>
+      </c>
+      <c r="J418" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="K418" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="L418" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="M418" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="N418" t="n">
+        <v>360.15</v>
+      </c>
+      <c r="O418" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="P418" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>360.97</v>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25406,7 +25526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B442"/>
+  <dimension ref="A1:B444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29829,6 +29949,26 @@
       </c>
       <c r="B442" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -29997,28 +30137,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3334419211375329</v>
+        <v>0.3285063541199019</v>
       </c>
       <c r="J2" t="n">
+        <v>417</v>
+      </c>
+      <c r="K2" t="n">
         <v>415</v>
       </c>
-      <c r="K2" t="n">
-        <v>413</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1625034761495099</v>
+        <v>0.1594630381523264</v>
       </c>
       <c r="M2" t="n">
-        <v>4.312468500582569</v>
+        <v>4.318420110883331</v>
       </c>
       <c r="N2" t="n">
-        <v>31.65875104460243</v>
+        <v>31.63049088347665</v>
       </c>
       <c r="O2" t="n">
-        <v>5.626610973277113</v>
+        <v>5.6240991175011</v>
       </c>
       <c r="P2" t="n">
-        <v>355.7037000702675</v>
+        <v>355.7555282303235</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30075,28 +30215,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5141297913845554</v>
+        <v>0.5058750779665609</v>
       </c>
       <c r="J3" t="n">
+        <v>417</v>
+      </c>
+      <c r="K3" t="n">
         <v>415</v>
       </c>
-      <c r="K3" t="n">
-        <v>413</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3258378161732413</v>
+        <v>0.3187863647358236</v>
       </c>
       <c r="M3" t="n">
-        <v>4.289894815949134</v>
+        <v>4.313857491587737</v>
       </c>
       <c r="N3" t="n">
-        <v>30.2163124257214</v>
+        <v>30.4082736738104</v>
       </c>
       <c r="O3" t="n">
-        <v>5.496936640140706</v>
+        <v>5.51436974402428</v>
       </c>
       <c r="P3" t="n">
-        <v>356.5010438411502</v>
+        <v>356.5877344192484</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30153,28 +30293,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3335336918244268</v>
+        <v>0.3291469438969761</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2205880744724878</v>
+        <v>0.2172343088308251</v>
       </c>
       <c r="M4" t="n">
-        <v>3.513650649828684</v>
+        <v>3.516136213811222</v>
       </c>
       <c r="N4" t="n">
-        <v>21.67562383727034</v>
+        <v>21.6664847440099</v>
       </c>
       <c r="O4" t="n">
-        <v>4.655708736301095</v>
+        <v>4.654727139587228</v>
       </c>
       <c r="P4" t="n">
-        <v>368.2886340167255</v>
+        <v>368.3347228920603</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30231,28 +30371,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4105364717461795</v>
+        <v>0.4015779858666922</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L5" t="n">
-        <v>0.265451678264978</v>
+        <v>0.2561750172502321</v>
       </c>
       <c r="M5" t="n">
-        <v>3.736341542460652</v>
+        <v>3.754053004903202</v>
       </c>
       <c r="N5" t="n">
-        <v>25.71849518971805</v>
+        <v>25.98838049770012</v>
       </c>
       <c r="O5" t="n">
-        <v>5.07134057126102</v>
+        <v>5.097880000323676</v>
       </c>
       <c r="P5" t="n">
-        <v>367.6461819973886</v>
+        <v>367.7403087526396</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30309,28 +30449,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4046400583268948</v>
+        <v>0.4006119710734198</v>
       </c>
       <c r="J6" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K6" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3349371854473147</v>
+        <v>0.3320035634522636</v>
       </c>
       <c r="M6" t="n">
-        <v>3.201425491608905</v>
+        <v>3.203252658742602</v>
       </c>
       <c r="N6" t="n">
-        <v>17.92851075962347</v>
+        <v>17.92192607866545</v>
       </c>
       <c r="O6" t="n">
-        <v>4.234207217369441</v>
+        <v>4.233429588249396</v>
       </c>
       <c r="P6" t="n">
-        <v>367.4939982930958</v>
+        <v>367.5363210127821</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30387,28 +30527,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4510356837212244</v>
+        <v>0.4478951828157176</v>
       </c>
       <c r="J7" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K7" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3706990385930161</v>
+        <v>0.3694685956401365</v>
       </c>
       <c r="M7" t="n">
-        <v>3.137839594332362</v>
+        <v>3.136288317624872</v>
       </c>
       <c r="N7" t="n">
-        <v>19.04433919737744</v>
+        <v>19.00147921312172</v>
       </c>
       <c r="O7" t="n">
-        <v>4.363982034492974</v>
+        <v>4.35906861762025</v>
       </c>
       <c r="P7" t="n">
-        <v>366.2801268623856</v>
+        <v>366.3131274179272</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30465,28 +30605,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3957055187735197</v>
+        <v>0.3951312382081765</v>
       </c>
       <c r="J8" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K8" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3372373920048011</v>
+        <v>0.3390811145985355</v>
       </c>
       <c r="M8" t="n">
-        <v>3.276797956527447</v>
+        <v>3.263721819692975</v>
       </c>
       <c r="N8" t="n">
-        <v>16.96968021249328</v>
+        <v>16.89011964997331</v>
       </c>
       <c r="O8" t="n">
-        <v>4.119427170431986</v>
+        <v>4.109759074443819</v>
       </c>
       <c r="P8" t="n">
-        <v>364.7875304719678</v>
+        <v>364.7935672787204</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30543,28 +30683,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3335874025544558</v>
+        <v>0.3346371247407345</v>
       </c>
       <c r="J9" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K9" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2173703717756459</v>
+        <v>0.220326863253707</v>
       </c>
       <c r="M9" t="n">
-        <v>3.685739573906034</v>
+        <v>3.67356649831877</v>
       </c>
       <c r="N9" t="n">
-        <v>22.09440894133001</v>
+        <v>21.99372523964593</v>
       </c>
       <c r="O9" t="n">
-        <v>4.700469012910308</v>
+        <v>4.689746820420686</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2834309933201</v>
+        <v>366.2724028973601</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30621,28 +30761,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2800251283380636</v>
+        <v>0.2811954742458633</v>
       </c>
       <c r="J10" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K10" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2002742757224347</v>
+        <v>0.203366357586332</v>
       </c>
       <c r="M10" t="n">
-        <v>3.334880062660649</v>
+        <v>3.32463639174486</v>
       </c>
       <c r="N10" t="n">
-        <v>17.26700733733009</v>
+        <v>17.19101904881381</v>
       </c>
       <c r="O10" t="n">
-        <v>4.155358869860711</v>
+        <v>4.146205379478181</v>
       </c>
       <c r="P10" t="n">
-        <v>367.8346039040375</v>
+        <v>367.8223091768928</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30699,28 +30839,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2490357524416136</v>
+        <v>0.2506822652134473</v>
       </c>
       <c r="J11" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K11" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1546254886072685</v>
+        <v>0.1577462019045364</v>
       </c>
       <c r="M11" t="n">
-        <v>3.51408899005485</v>
+        <v>3.505675281369164</v>
       </c>
       <c r="N11" t="n">
-        <v>18.69814971382081</v>
+        <v>18.62244597774485</v>
       </c>
       <c r="O11" t="n">
-        <v>4.324135718709672</v>
+        <v>4.315373214189573</v>
       </c>
       <c r="P11" t="n">
-        <v>367.685629807921</v>
+        <v>367.6683335411437</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30777,28 +30917,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2310390341376764</v>
+        <v>0.2337312581612748</v>
       </c>
       <c r="J12" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K12" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1033033283359729</v>
+        <v>0.1064001962500282</v>
       </c>
       <c r="M12" t="n">
-        <v>4.267609152801437</v>
+        <v>4.258608847481202</v>
       </c>
       <c r="N12" t="n">
-        <v>25.55107234658445</v>
+        <v>25.46476455313632</v>
       </c>
       <c r="O12" t="n">
-        <v>5.054806855517277</v>
+        <v>5.046262434033363</v>
       </c>
       <c r="P12" t="n">
-        <v>362.7776183094959</v>
+        <v>362.7493347451561</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30855,28 +30995,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2459454532111184</v>
+        <v>0.2476335917338069</v>
       </c>
       <c r="J13" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K13" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1090904813380589</v>
+        <v>0.1114845890975892</v>
       </c>
       <c r="M13" t="n">
-        <v>4.414760452687626</v>
+        <v>4.401013585990492</v>
       </c>
       <c r="N13" t="n">
-        <v>27.24153057876423</v>
+        <v>27.1253078999474</v>
       </c>
       <c r="O13" t="n">
-        <v>5.219341967984492</v>
+        <v>5.208196223256897</v>
       </c>
       <c r="P13" t="n">
-        <v>358.1070819688686</v>
+        <v>358.0893480418268</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30933,28 +31073,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1838508369193133</v>
+        <v>0.187213351236221</v>
       </c>
       <c r="J14" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K14" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0574420414025566</v>
+        <v>0.05996167605728742</v>
       </c>
       <c r="M14" t="n">
-        <v>4.725661256356049</v>
+        <v>4.716973805575487</v>
       </c>
       <c r="N14" t="n">
-        <v>30.8258267300553</v>
+        <v>30.7351861029342</v>
       </c>
       <c r="O14" t="n">
-        <v>5.552101109494973</v>
+        <v>5.543932368178223</v>
       </c>
       <c r="P14" t="n">
-        <v>352.2645472778996</v>
+        <v>352.2294201875931</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31011,28 +31151,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2873788991600599</v>
+        <v>0.2898987556520325</v>
       </c>
       <c r="J15" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K15" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1057421529851963</v>
+        <v>0.108398012136518</v>
       </c>
       <c r="M15" t="n">
-        <v>5.300879722537394</v>
+        <v>5.284913545994861</v>
       </c>
       <c r="N15" t="n">
-        <v>38.81768899073598</v>
+        <v>38.66631895288413</v>
       </c>
       <c r="O15" t="n">
-        <v>6.230384337321092</v>
+        <v>6.218224742873494</v>
       </c>
       <c r="P15" t="n">
-        <v>350.1035725307822</v>
+        <v>350.0772527056853</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31089,28 +31229,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2715067864552312</v>
+        <v>0.2753185662958993</v>
       </c>
       <c r="J16" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K16" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07468830837232088</v>
+        <v>0.07732996747544751</v>
       </c>
       <c r="M16" t="n">
-        <v>5.866174513693101</v>
+        <v>5.852903658468092</v>
       </c>
       <c r="N16" t="n">
-        <v>50.75772131476033</v>
+        <v>50.58945525509822</v>
       </c>
       <c r="O16" t="n">
-        <v>7.124445333831984</v>
+        <v>7.112626466720871</v>
       </c>
       <c r="P16" t="n">
-        <v>352.7802747221859</v>
+        <v>352.7404566435043</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31167,28 +31307,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2155718715744487</v>
+        <v>0.2192970888448019</v>
       </c>
       <c r="J17" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K17" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03740764725253343</v>
+        <v>0.03903838030887319</v>
       </c>
       <c r="M17" t="n">
-        <v>6.732732380019706</v>
+        <v>6.714523288856832</v>
       </c>
       <c r="N17" t="n">
-        <v>66.46170966068087</v>
+        <v>66.21713729266121</v>
       </c>
       <c r="O17" t="n">
-        <v>8.152405145764094</v>
+        <v>8.137391307578936</v>
       </c>
       <c r="P17" t="n">
-        <v>352.4339039580099</v>
+        <v>352.3949925978698</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31226,7 +31366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R416"/>
+  <dimension ref="A1:R418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69445,6 +69585,190 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-36.835736332079264,175.8022418008806</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-36.836107327740564,175.8030111206941</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-36.83641125158598,175.80383215727454</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-36.836824659216845,175.80456876996325</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-36.83717884363585,175.80535360168304</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-36.83757616409686,175.80610551155067</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-36.83799099249201,175.8068403246938</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-36.83839154485563,175.80758285772083</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-36.83878160825307,175.80833112913373</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-36.83916342584673,175.80908970902405</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-36.83957735558282,175.80982813891043</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-36.84000743902335,175.81055319747824</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-36.8404399254397,175.81127593868564</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-36.840873882025264,175.81199129933782</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-36.84130745042488,175.8127067788423</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-36.841752504087594,175.8134113295933</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-36.835721402265875,175.80225331331312</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-36.836095919798424,175.80301991733427</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-36.83640512649665,175.8038368802739</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-36.836821213844615,175.80457142664144</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-36.837176642234915,175.80535535123488</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-36.83758028953527,175.80610209868985</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-36.83799525448223,175.80683676265247</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-36.838393960434225,175.80758090101395</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-36.83878536918683,175.80832825502065</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-36.839169997206,175.80908482037756</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-36.83958428463908,175.80982290311047</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-36.84001349536196,175.8105485490856</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-36.84044710069422,175.81126993407256</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-36.840885616784234,175.8119801347849</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-36.841318911963825,175.81269590771987</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-36.841767805081965,175.81339749189422</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
